--- a/bakup/customers/mohammad saleh.xlsx
+++ b/bakup/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="220">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -667,6 +667,18 @@
   </si>
   <si>
     <t>1405/05/26</t>
+  </si>
+  <si>
+    <t>1405/05/31</t>
+  </si>
+  <si>
+    <t>پچ پچ</t>
+  </si>
+  <si>
+    <t>مزه</t>
+  </si>
+  <si>
+    <t>1405/06/02</t>
   </si>
 </sst>
 </file>
@@ -1215,7 +1227,7 @@
       </c>
       <c r="H2" s="9">
         <f>B218</f>
-        <v>208000</v>
+        <v>518000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4016,37 +4028,55 @@
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="8">
         <f>A205+B206-C206</f>
-        <v>208000</v>
-      </c>
-      <c r="B206" s="8"/>
+        <v>258000</v>
+      </c>
+      <c r="B206" s="8">
+        <v>50000</v>
+      </c>
       <c r="C206" s="8"/>
-      <c r="D206" s="1"/>
-      <c r="E206" s="1"/>
+      <c r="D206" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="207" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="8">
         <f t="shared" ref="A207" si="15">A206+B207-C207</f>
-        <v>208000</v>
-      </c>
-      <c r="B207" s="8"/>
+        <v>329000</v>
+      </c>
+      <c r="B207" s="8">
+        <v>71000</v>
+      </c>
       <c r="C207" s="8"/>
-      <c r="D207" s="1"/>
-      <c r="E207" s="1"/>
+      <c r="D207" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="208" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="8">
         <f>A207+B208-C208</f>
-        <v>208000</v>
-      </c>
-      <c r="B208" s="8"/>
+        <v>518000</v>
+      </c>
+      <c r="B208" s="8">
+        <v>189000</v>
+      </c>
       <c r="C208" s="8"/>
-      <c r="D208" s="1"/>
-      <c r="E208" s="1"/>
+      <c r="D208" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="209" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="8">
         <f t="shared" ref="A209:A215" si="16">A208+B209-C209</f>
-        <v>208000</v>
+        <v>518000</v>
       </c>
       <c r="B209" s="8"/>
       <c r="C209" s="8"/>
@@ -4056,7 +4086,7 @@
     <row r="210" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="8">
         <f t="shared" si="16"/>
-        <v>208000</v>
+        <v>518000</v>
       </c>
       <c r="B210" s="8"/>
       <c r="C210" s="8"/>
@@ -4066,7 +4096,7 @@
     <row r="211" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="8">
         <f t="shared" si="16"/>
-        <v>208000</v>
+        <v>518000</v>
       </c>
       <c r="B211" s="8"/>
       <c r="C211" s="8"/>
@@ -4076,7 +4106,7 @@
     <row r="212" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="8">
         <f t="shared" si="16"/>
-        <v>208000</v>
+        <v>518000</v>
       </c>
       <c r="B212" s="8"/>
       <c r="C212" s="8"/>
@@ -4086,7 +4116,7 @@
     <row r="213" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="8">
         <f t="shared" si="16"/>
-        <v>208000</v>
+        <v>518000</v>
       </c>
       <c r="B213" s="8"/>
       <c r="C213" s="8"/>
@@ -4096,7 +4126,7 @@
     <row r="214" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <f t="shared" si="16"/>
-        <v>208000</v>
+        <v>518000</v>
       </c>
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
@@ -4106,7 +4136,7 @@
     <row r="215" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <f t="shared" si="16"/>
-        <v>208000</v>
+        <v>518000</v>
       </c>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -4116,7 +4146,7 @@
     <row r="216" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B216" s="9">
         <f>SUM(B196:B215)+B190</f>
-        <v>11136000</v>
+        <v>11446000</v>
       </c>
       <c r="C216" s="9">
         <f>SUM(C196:C215)+C190</f>
@@ -4127,7 +4157,7 @@
     <row r="218" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B218" s="15">
         <f>A215</f>
-        <v>208000</v>
+        <v>518000</v>
       </c>
       <c r="C218" s="17" t="s">
         <v>184</v>
